--- a/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-27T18:48:52Z by SETUP | data f16a494a971dde84</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-28T03:17:00Z by SETUP | data 697afb309489c934</t>
         </is>
       </c>
     </row>
@@ -1783,6 +1783,419 @@
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="5" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>TQ-IEC-016</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>HRSG temperature cross in PER-001 Rev A (IP SH and LP SH)</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Rating the HRSG section by section (EPC off-design check) shows two impossible sections in PER-001 Rev A section 5: the IP superheater sits in gas at 299.9 -&gt; 295.1 degC but delivers steam at 330 degC, and the LP superheater sits in gas at 201.5 -&gt; 197.4 degC but delivers steam at 300 degC. Please correct the HRSG arrangement and reissue the heat balance and the HRSG datasheet.</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>IP SH directly after the HP evaporator; LP SH after the IP evaporator with a feasible LP steam temperature.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>process_stream:SRC-NG-100_10
+process_stream:SRC-NG-100_13
+source:SRC-IECE-0001
+source:SRC-EPCE-0005</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed - a drafting error in the Rev 0/A section order. Corrected arrangement in PER-001 Rev B and DS-104 Rev A: IP superheater directly after the HP evaporator (gas 371.6 -&gt; 366.9 degC, steam 330 degC), LP superheater directly after the IP evaporator (gas 261.0 -&gt; 258.2 degC) with LP steam at 250 degC. Effect: ST output 200.73 MW (-0.16 MW), LP steam 11.90 kg/s. IP-SH duty and all pinch points unchanged.</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>requirement changed</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="5" t="inlineStr">
+        <is>
+          <t>source (PER-001 Rev B)
+source (DS-104 Rev A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>TQ-IEC-017</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Off-design heat balances for all design and guarantee cases</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>The plant HMB must cover all design and guarantee cases, not only SRC. Please provide rated off-design heat balances (fixed HRSG and condenser surfaces, sliding pressure, attemperation) for: SRC-NG-100; SRC-NG-GT80; SRC-NG-060 (60 % plant net load, PG-03); SRC-NG-MEL (minimum emissions-compliant load, PG-11); SRC-LDO-100 (LDO, PG-15/16); WIN-NG-100 (-4.8 degC, 99.6 %); MIN-NG-100 (-8 degC); SUM-NG-100 (32.8 degC, 0.4 %); MAX-NG-100 (40 degC with 27 degC seawater). Stream numbering as PER-001, with added streams for LDO, injection water and attemperation spray.</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>IEC-ALP-PER-003 case book with one stream table per case.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>guarantee:PG-03
+guarantee:PG-11
+guarantee:PG-15
+guarantee:PG-16
+design_parameter:DP-OWNR-0001
+design_parameter:DP-OWNR-0002
+design_parameter:DP-CASE-0007
+design_parameter:DP-CASE-0008
+design_parameter:DP-OWNR-0012</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>IEC-ALP-PER-003 Rev 0 issued with the nine cases, one stream table each; the rating model reproduces PER-001 Rev B exactly at SRC. Attemperation spray is in service at part load and at high ambient (streams 29/30).</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>confirmed as is</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>source (PER-003 Rev 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>TQ-IEC-018</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>LDO case: net output below PG-15 and implausible air flow</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>The EPC HMB of PER-003 case SRC-LDO-100 gives 558.8 MW net against PG-15 (&gt;= 560 MW), margin -0.21 %. In addition the case implies a compressor air flow of 701 kg/s on LDO against 776 kg/s on gas at the same ambient with the IGV fully open, which is not plausible: with the gas-operation air flow the stated LDO rating and water/fuel ratio 1.02 give an exhaust temperature of about 553 degC and about 543 MW / 6,300 kJ/kWh net, missing PG-15 and PG-16. Please re-rate the LDO case with the real air flow and propose how the LDO guarantees are met.</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Reduce water injection and size the SCR for the higher GT-outlet NOx on LDO (ER-03.11 already requires an SCR designed for LDO).</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>guarantee:PG-15
+guarantee:PG-16
+hmb_case:SRC-LDO-100
+requirement:ER-03.11
+source:SRC-IECE-0004</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Agreed - the Rev 0 LDO case back-calculated the air flow. PER-003 Rev A: gas-operation air flow (776.0 kg/s), LDO rating 400.5 MW / 8,640 kJ/kWh, water/fuel 0.60 (13.4 kg/s) with GT-outlet NOx &lt;= 150 mg/Nm3 and the IEC SCR sized for 67 % removal on LDO (DS-104 Rev B: catalyst +35 %, ammonia 480 kg/h on LDO). Exhaust 811.9 kg/s at 592.7 degC; ST 178.37 MW; about 567 MW / 6,100 kJ/kWh net with the EPC auxiliaries. New IEC guarantees IG-09/IG-10 on LDO.</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>contractor proposal accepted</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="n"/>
+      <c r="Q22" s="5" t="inlineStr">
+        <is>
+          <t>source (PER-003 Rev A, DS-101 Rev A, DS-104 Rev B)
+guarantee/IG-09
+guarantee/IG-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>TQ-IEC-019</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Minimum environmental load: 44.7 % against PG-11 (40 %)</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>With the GT minimum emissions-compliant load of 40 % (DS-101), case SRC-NG-MEL gives 274.3 MW net = 44.7 % of the SRC net output, against PG-11 (&lt;= 40 % of plant net output). Please provide a lower MECL.</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>IEC low-load extension to reach &lt;= 35 % plant load; as part of the power island scope (back-to-back PG-11).</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>guarantee:PG-11
+hmb_case:SRC-NG-MEL
+source:SRC-EPCE-0002</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>IEC includes the DLN-H2 low-load extension in the power island scope at no price change (back-to-back PG-11): MECL 30 % GT load with CO &lt;= 30 mg/Nm3 at the stack (oxidation catalyst). PER-003 Rev A case SRC-NG-MEL at 30 % GT load: about 213 MW net = 34.8 % of the SRC net output. New IEC guarantee IG-08.</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>contractor proposal accepted</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>guarantee/IG-08
+source (DS-101 Rev A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>TQ-IEC-020</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>TQ-IEC-018</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>commercial</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>IG-10 does not cover PG-16</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>At the IG-09/IG-10 limits (572.0 MW / 6,030 kJ/kWh gross) and the EPC auxiliaries of case SRC-LDO-100 the plant is 560.2 MW / 6,157 kJ/kWh net against PG-16 (6,150 kJ/kWh). Please tighten IG-10.</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>IG-10 &lt;= 6,020 kJ/kWh (expected 5,977 kJ/kWh).</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>guarantee:IG-09
+guarantee:IG-10
+guarantee:PG-16
+hmb_case:SRC-LDO-100</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Accepted: IG-10 &lt;= 6,020 kJ/kWh.</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>contractor proposal accepted</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="n"/>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>guarantee/IG-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1796,7 +2209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1891,78 +2304,116 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" s="6" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Round 4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Round 5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
           <t>By outcome</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>confirmed as is</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>contractor proposal accepted</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>6</v>
-      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>follow up required</t>
+          <t>confirmed as is</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>contractor proposal accepted</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>follow up required</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>requirement changed</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1</v>
+      <c r="B13" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-28T03:17:00Z by SETUP | data 697afb309489c934</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-28T03:43:27Z by SETUP | data 739c56375ca05fc7</t>
         </is>
       </c>
     </row>
@@ -2196,6 +2196,137 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>TQ-IEC-021</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Tie-in register: interface conditions IF-01..IF-44 for agreement</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>The EPC tie-in register (engine tie_in_register, draft) checks every terminal point against the nine PER-003 Rev A cases and against its upstream point. Please confirm or correct: (1) IF-06 (200 bar(a) / 605 degC), IF-10 (48 bar(a) / 605 degC) and IF-12 (8 bar(a)) are below the design of the HRSG outlets feeding them (IF-05 210 bar(a) / 610 degC, IF-09 50 bar(a) / 610 degC, IF-11 10 bar(a)); the EPC piping between them is designed for the HRSG side. State the ST valve casing design conditions, or the safety valve set points that protect the ST side. (2) HMB streams 29 and 30 (HP and reheat attemperation spray water from the EPC BFP discharge/interstage to the HRSG) cross the scope boundary but have no terminal point in IF-001 Rev 0. (3) PER-003 stream 28 (water injection) is at 60 bar(a), IF-03 is 4 in CL150 / 16 barg: confirm IF-03 is at the skid inlet upstream of IEC injection pumps, the pressure required there, and that the pump power is in the IEC auxiliaries. (4) IF-36: the EPC estimates 169 kA prospective short-circuit current at the GT generator bus (96 kA from the system via the GSU + 73 kA from the generator); state the IPB tap-off rating. (5) Confirm the operating envelopes, scope breaks, isolation, protection and dates of the attached draft (dates per the EPC commissioning sequence DEC-EPCE-0004) and re-issue IF-001.</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>(1) ST valve casings designed for the HRSG outlet conditions; (2) new IF-45 / IF-46 at the inlet of the IEC spray control stations; (3) IF-03 at the skid inlet, 3.0-6.0 barg; (4) tap-off rated &gt;= 170 kA; (5) IF-001 Rev A with the agreed data.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>tie_in:IF-03
+tie_in:IF-06
+tie_in:IF-10
+tie_in:IF-12
+tie_in:IF-36
+process_stream:SRC-LDO-100_28
+process_stream:MAX-NG-100_29
+process_stream:MAX-NG-100_30
+source:SRC-EPCE-0008
+source:SRC-IECE-0005</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>(1) The IF-001 Rev 0 values at IF-06/IF-10/IF-12 were the ST rated inlet conditions (IEC 60045-1). Valve casing design: main stop valve 215 bar(a) / 610 degC, IP stop/control valves 52 bar(a) / 610 degC, LP admission valve 10 bar(a) / 330 degC; the HRSG safety valves (HP SH &lt;= 196 bar(a), HRH &lt;= 48 bar(a), LP SH 8.0 bar(a)) protect both sides. (2) Accepted: IF-45 (HP spray, 3 in CL2500) and IF-46 (reheat spray, 2 in CL600) at the inlet of the IEC spray control stations. (3) Confirmed: IF-03 is the water injection skid inlet, 3.0-6.0 barg; stream 28 in PER-003 is the skid discharge; the injection pumps are in the IEC GT auxiliaries. (4) IPB tap-off rated 200 kA symmetrical / 550 kA peak. (5) Draft data confirmed with the corrections above; IEC-ALP-IF-001 Rev A issued.</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>contractor proposal accepted</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="n"/>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>tie_in/IF-01
+tie_in/IF-02
+tie_in/IF-03
+tie_in/IF-04
+tie_in/IF-05
+tie_in/IF-06
+tie_in/IF-07
+tie_in/IF-08
+tie_in/IF-09
+tie_in/IF-10
+tie_in/IF-11
+tie_in/IF-12
+tie_in/IF-13
+tie_in/IF-14
+tie_in/IF-15
+tie_in/IF-16
+tie_in/IF-17
+tie_in/IF-18
+tie_in/IF-19
+tie_in/IF-20
+tie_in/IF-21
+tie_in/IF-22
+tie_in/IF-23
+tie_in/IF-24
+tie_in/IF-25
+tie_in/IF-26
+tie_in/IF-27
+tie_in/IF-28
+tie_in/IF-29
+tie_in/IF-30
+tie_in/IF-31
+tie_in/IF-32
+tie_in/IF-33
+tie_in/IF-34
+tie_in/IF-35
+tie_in/IF-36
+tie_in/IF-37
+tie_in/IF-38
+tie_in/IF-39
+tie_in/IF-40
+tie_in/IF-41
+tie_in/IF-42
+tie_in/IF-43
+tie_in/IF-44
+tie_in/IF-45
+tie_in/IF-46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2209,7 +2340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2342,77 +2473,96 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Round 6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="B8" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E8" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>By outcome</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>confirmed as is</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>8</v>
-      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>contractor proposal accepted</t>
+          <t>confirmed as is</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>follow up required</t>
+          <t>contractor proposal accepted</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>follow up required</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>requirement changed</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B14" t="n">
         <v>2</v>
       </c>
     </row>

--- a/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-28T03:43:27Z by SETUP | data 739c56375ca05fc7</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-28T03:56:48Z by SETUP | data 86fb906a41f93ae0</t>
         </is>
       </c>
     </row>
@@ -2327,6 +2327,96 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>TQ-IEC-022</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Codes and standards back-to-back, and IEC deliverables for permits</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>The codes and standards register (Appendix A.19, proposed to the Owner in TQ-033) names IEC as responsible for 62 entries (power island design, tests, Turkish regulations applicable to the IEC supply). Please confirm compliance back-to-back and state any deviation, in particular: (1) ER-06.02 allows ASME Section I or EN 12952 - which code, which PED module; ER-06.05 cites EN 12952-3 for the cyclic assessment; (2) HEI edition for the condenser (ER-07.07: 11th or later); (3) GT enclosure fire protection (ER-10.05: water mist or CO2); (4) IEC 62443 SL2 for the TCS. (5) Confirm the IEC deliverables for the permits PMT-004, 005, 008, 009, 013, 014, 015, 016, 018 and 021 with the dates of the permits register.</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>ASME Section I with PED module G; EN 12952-3 for fatigue of thick-walled parts; HEI 12th edition; CO2 per NFPA 12; SL2; IEC deliverables 30 days before each apply-by date.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>reference:REF-CONS-0042
+reference:REF-CONS-0043
+reference:REF-CONS-0045
+reference:REF-CONS-0082
+requirement:ER-06.02
+requirement:ER-06.05
+requirement:ER-07.07
+requirement:ER-10.05
+permit:PMT-004
+permit:PMT-015</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed back-to-back for all entries naming IEC, with: (1) HRSG to ASME Section I, PED module G by a notified body; EN 12952-3 for the low-cycle fatigue of the HP drum and SH/RH outlet headers; (2) HEI 12th edition; (3) GT enclosure CO2 total flooding per NFPA 12; (4) TCS system SL2 (IEC 62443-3-3) with certified components; please add ISO 20816-2 for the vibration limits of the turbines and generators. (5) IEC deliverables for the permits 30 days before each apply-by date of the permits register: generator/GSU data and models (PMT-004, PMT-021), foundation loads (PMT-005), heavy piece list and transport drawings (PMT-008, PMT-009), NDT source licences of IEC's site subcontractors (PMT-013), GT gas demand (PMT-014), inventories (PMT-015), declarations of conformity and notified body certificates (PMT-016), GT emission data (PMT-018).</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>contractor proposal accepted</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="5" t="inlineStr">
+        <is>
+          <t>reference/REF-CONS-0043
+reference/REF-CONS-0042
+reference/REF-CONS-0045
+reference/REF-CONS-0048
+reference/REF-CONS-0082</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2479,10 +2569,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -2498,10 +2588,10 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
@@ -2543,7 +2633,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">

--- a/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-28T03:56:48Z by SETUP | data 86fb906a41f93ae0</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-28T15:04:30Z by SETUP | data 8002a4a11746e259</t>
         </is>
       </c>
     </row>
@@ -2417,6 +2417,85 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>TQ-IEC-023</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Engineering start: project KKS and document numbering, VDRL dates, generator delivery</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>(1) ER-01.06 requires KKS for all systems, equipment and documents. Please confirm that the power island (main groups MB, MK, HA, MA, BA/BAT for the GSUs, CJ/MBY for the TCS) is tagged with the project KKS key list (proposal ALP-EPC-00000-GE-PRC-0001) to component level B, and that your internal part numbers stay below component level. (2) Please confirm that every IEC deliverable carries the project document number ALP-IEC-&lt;KKS&gt;-&lt;DISC&gt;-&lt;TYPE&gt;-&lt;NNNN&gt; as primary number and the IEC number as secondary (vendor reference), as allocated in the MDL. (3) Please confirm the VDRL first-issue and final dates in the MDL (weeks after NTP). (4) The MDL / AWP timeline shows the GT generator (MR-EL-101, 52 weeks + 4 weeks sea transport) on site 2027-11-29, while GT erection CWP-01-ME-01 starts 2027-11-15 (generator set directly after the GT). Can the GT generator ship with the GT (50 weeks)?</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Ship the GT generator with the GT; ST generator unchanged (needed at CWP-02-ME-01 start).</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>requirement:ER-01.06
+requirement:ER-17.01
+source:SRC-EPCE-0009</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>(1) Confirmed. IEC tags the power island with the project KKS to component level (B), systems and equipment units per the project key list; IEC part numbers are kept as vendor attributes below component level. IEC checks the key titles of its main groups against its VGB-S-811 licence copy and reports deviations with the KKS manual review (IFR). (2) Confirmed: project number primary, IEC number as vendor reference on the title block. (3) Confirmed: the VDRL dates in the MDL are the IEC commitment. (4) Confirmed with an improvement: generator shop tests are brought forward; the GT generators leave the works in week 49 together with the GT (sea transport 4 weeks), on site 2027-11-08. The ST generator follows the ST train (no change).</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>contractor proposal accepted</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="n"/>
+      <c r="Q27" s="5" t="inlineStr">
+        <is>
+          <t>mr/MR-EL-101</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2430,7 +2509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2582,77 +2661,96 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Round 7</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="B9" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E9" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>By outcome</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>confirmed as is</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>8</v>
-      </c>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>contractor proposal accepted</t>
+          <t>confirmed as is</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>follow up required</t>
+          <t>contractor proposal accepted</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>follow up required</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>requirement changed</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B15" t="n">
         <v>2</v>
       </c>
     </row>

--- a/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-28T15:04:30Z by SETUP | data 8002a4a11746e259</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-28T17:23:01Z by SETUP | data 2cd2ed22bfcdf89a</t>
         </is>
       </c>
     </row>
@@ -2496,6 +2496,78 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>TQ-IEC-024</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Power island VDRL completed to the rule-based MDL Rev B</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>MDL Rev B derives the supplier documents per package from rules (mdl_rule DL-V-*). For the six IEC packages this adds 83 documents to the 37 committed in TQ-IEC-023: certified datasheets, GA, foundation loads, P&amp;IDs, design calculations, electrical schematics, I/O lists, instrument lists, logic diagrams (TCS), ITPs, FAT procedures and reports, erection and O&amp;M manuals, spare parts and special tools lists, manufacturing record books and commissioning procedures. Dates: weeks after the PO (NTP) for design documents, weeks before delivery for FAT, erection and O&amp;M documents (rule fields po_weeks_ifr / po_weeks_final). Please confirm the list and the timing, and that IEC provides the heavy and oversized piece data and the transport drawings for the Harbour Master and abnormal load permits (PMT-008, PMT-009).</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>requirement:ER-15.03
+requirement:ER-16.01
+requirement:ER-17.04
+requirement:ER-17.06</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed. The rule-based VDRL is accepted as the IEC document commitment; documents already committed in TQ-IEC-023 keep their dates. IEC provides the heavy piece data (dimensions, weights, centre of gravity, lifting points) and the transport drawings of the GT, generators, HRSG modules, ST and GSUs 12 weeks after NTP as input to the EPC heavy piece list and route survey. TCS logic diagrams are issued in two batches (protection first); the rule dates (PO + 20 / 32 weeks) are met.</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>confirmed as is</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="n"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2509,7 +2581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2680,77 +2752,96 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Round 8</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="D9" s="6" t="n">
+      <c r="B10" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E10" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>By outcome</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>confirmed as is</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>8</v>
-      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>contractor proposal accepted</t>
+          <t>confirmed as is</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>follow up required</t>
+          <t>contractor proposal accepted</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>follow up required</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>requirement changed</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>2</v>
       </c>
     </row>

--- a/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-28T17:23:01Z by SETUP | data 2cd2ed22bfcdf89a</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-28T18:13:10Z by SETUP | data ae00813907e24242</t>
         </is>
       </c>
     </row>

--- a/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-28T18:13:10Z by SETUP | data ae00813907e24242</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-28T19:00:23Z by EPCE | data 9f2f099cc0049c68</t>
         </is>
       </c>
     </row>
@@ -2568,6 +2568,62 @@
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="5" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>TQ-IEC-025</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>EPC review of the power island datasheets: heat balance consistency, missing design data and tags</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Review of the IEC datasheets against heat balance Rev B and the plant equipment list (review codes 2 on ALP-IEC-20MAA-ME-DSH-0001 Rev 0, ALP-IEC-10HAA-ME-DSH-0001 Rev B, ALP-IEC-10MBA-ME-DSH-0001 Rev A, ALP-IEC-10MKA-EL-DSH-0001 Rev 0, ALP-IEC-20MAG-ME-DSH-0001 Rev 0 and the GT / ST GA drawings): (1) update the ST datasheet LP flows to heat balance Rev B; (2) give the HRSG design temperatures per section; (3) state whether the GT 425 MW is shaft output and how it relates to IG-03 (418 MW at the terminals); (4) provide tags and ratings of the condensate preheater recirculation pumps, the HP / IP / LP bypass valves and dump devices, the generator neutral earthing and excitation transformers and the generator protection panels; (5) confirm the condenser circulating water design flow and give the water-side design and test pressure; (6) give the SFC starting load profile; (7) state the heaviest maintenance lift weights on the GT and ST GA drawings.</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>guarantee:IG-03
+source:SRC-EPCE-0004
+source:SRC-IECE-0007
+source:SRC-EPCE-0006</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr"/>
+      <c r="O29" s="4" t="n"/>
+      <c r="P29" s="4" t="n"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2581,7 +2637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2771,77 +2827,106 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Round 9</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B11" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C11" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="C10" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D10" s="6" t="n">
+      <c r="D11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>By outcome</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>confirmed as is</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>9</v>
-      </c>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>contractor proposal accepted</t>
+          <t>confirmed as is</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>follow up required</t>
+          <t>contractor proposal accepted</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>follow up required</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>requirement changed</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B18" t="n">
         <v>2</v>
       </c>
     </row>

--- a/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-28T19:00:23Z by EPCE | data 9f2f099cc0049c68</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-29T02:54:29Z by SETUP | data 849c15aaf34be70d</t>
         </is>
       </c>
     </row>

--- a/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
+++ b/output/clarification_register/ALP_clarification_register_ALP-CA-001.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine clarification_register v1.1.0 | generated 2026-09-29T02:54:29Z by SETUP | data 849c15aaf34be70d</t>
+          <t>engine clarification_register v1.1.0 | generated 2026-09-29T03:49:36Z by EPCE | data 852c90d1bca64236</t>
         </is>
       </c>
     </row>
@@ -2612,17 +2612,94 @@
 source:SRC-EPCE-0006</t>
         </is>
       </c>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="4" t="n"/>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>(1) DS-103 Rev A per heat balance Rev B. (2) DS-104 Rev C with design temperatures. (3) 425.0 MW is the expected output at the generator terminals at SRC; IG-03 (418 MW) is guaranteed 1.6 % below it (DS-101 Rev B). (4) Tags: CPH recirculation pumps 10HAA10AP001 / AP002 (2 x 100 %, 45 m3/h, 60 m, 30 kW, 400 V), bypass valves 10LBA10AA501 / 10LBB10AA501 / 10LBD10AA501, neutral earthing transformers 10MKA20 / 20MKA20, excitation transformers 10MKC30 / 20MKC20, generator protection panels 10MKA30 / 20MKA30 (DS-102 Rev A). (5) Condenser design flow 10,197 kg/s; water side 4.0 barg design, 6.0 barg test (DS-105 Rev A). (6) SFC: 8.5 MW from 10.5 kV for about 25 min per start (purge, light-off, acceleration to 3,000 rpm), none in operation. (7) The GT and ST GA drawings state the lift weights in table 1 (no change).</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>2026-12-04</t>
+        </is>
+      </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="N29" s="4" t="inlineStr"/>
-      <c r="O29" s="4" t="n"/>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>confirmed as is</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>technical_only</t>
+        </is>
+      </c>
       <c r="P29" s="4" t="n"/>
       <c r="Q29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>TQ-IEC-026</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>2026-12-11</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Condenser CW temperature rise above the EIA limit in the cold cases</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>With the constant CW flow of the heat balance (10,197 kg/s, 36,113 m3/h) the condenser rise is 7.20 K in MIN-NG-100 and 7.28 K in WIN-NG-100 against the EIA limit of 7 K (DP-CASE-0015; steady state, TQ-041). The EPC CW pumps deliver 38,000 m3/h (DEC-EPCE-0002), which would give about 6.9 K but a tube velocity of 2.21 m/s (ER-07.07: 1.8 - 2.2 m/s). Please (a) set the condenser design CW flow so that the rise is at most 6.8 K in every steady-state case, with the tube count adjusted to keep 1.8 - 2.2 m/s, and (b) re-issue the heat balance cases and DS-105.</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Design CW flow about 38,700 m3/h (rise 6.8 K in WIN-NG-100), about 21,000 tubes; EPC re-rates the CW pumps.</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>design_parameter:DP-CASE-0015
+requirement:ER-07.07
+hmb_case:WIN-NG-100
+hmb_case:MIN-NG-100
+equipment:00PAC10AP001</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr"/>
+      <c r="O30" s="4" t="n"/>
+      <c r="P30" s="4" t="n"/>
+      <c r="Q30" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
@@ -2637,7 +2714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2836,84 +2913,93 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
         <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Round 10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B12" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="C12" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="C11" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D11" s="6" t="n">
+      <c r="D12" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E12" s="6" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>By outcome</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>confirmed as is</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>9</v>
-      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>contractor proposal accepted</t>
+          <t>confirmed as is</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>follow up required</t>
+          <t>contractor proposal accepted</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>follow up required</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2923,10 +3009,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>requirement changed</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>2</v>
       </c>
     </row>
